--- a/outputs/evaluation/architecture/design/v4/CF_M05/run_2/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v4/CF_M05/run_2/CF_M05_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.8341</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -589,10 +591,8 @@
           <t>fixedType</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" t="n">
+        <v>0.9412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1215,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.76</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1236,7 +1235,6 @@
           <t>['AU_07', 'AU_06']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_12</t>
@@ -1247,7 +1245,6 @@
           <t>spring boot, angular</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1266,7 +1263,6 @@
           <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU25</t>
@@ -1317,14 +1313,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1351,13 +1344,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1398,14 +1389,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1431,13 +1419,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1458,7 +1444,6 @@
       <c r="D5" t="n">
         <v>0.7902</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1479,7 +1464,6 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_11</t>
@@ -1490,7 +1474,6 @@
           <t>angular, spring boot</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1509,7 +1492,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -1560,14 +1542,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1596,13 +1575,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1643,14 +1620,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1679,13 +1653,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1726,14 +1698,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1758,13 +1727,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1785,7 +1752,6 @@
       <c r="D9" t="n">
         <v>0.9520999999999999</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1806,7 +1772,6 @@
           <t>['AU_01', 'AU_02', 'AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_10</t>
@@ -1817,7 +1782,6 @@
           <t>leader, portal, access control, communication log, scheduler</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1836,7 +1800,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -1892,13 +1855,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -1925,13 +1886,11 @@
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU35</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1977,13 +1936,11 @@
           <t>['AU_07']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2005,14 +1962,11 @@
       <c r="P11" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2058,13 +2012,11 @@
           <t>['AU_12']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>REST</t>
@@ -2089,13 +2041,11 @@
           <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU28</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2141,13 +2091,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2172,13 +2120,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2224,13 +2170,11 @@
           <t>['AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -2256,13 +2200,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2308,13 +2250,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -2334,14 +2274,11 @@
       <c r="P15" t="n">
         <v>62</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2387,13 +2324,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -2417,13 +2352,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2464,14 +2397,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2490,14 +2420,11 @@
       <c r="P17" t="n">
         <v>56</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2538,14 +2465,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2566,7 +2490,6 @@
       <c r="P18" t="n">
         <v>61</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -2577,7 +2500,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2651,7 +2573,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
@@ -2682,7 +2603,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>leader, portal, access control, communication log, scheduler</t>
@@ -2723,7 +2643,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>The data format used is JSON.</t>
@@ -2815,7 +2734,6 @@
           <t>Client (Frontend)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The client, also called the frontEnd, is responsible for the presentation and user experience
@@ -2828,7 +2746,6 @@
           <t>AU_11</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.8304</v>
       </c>
@@ -2849,7 +2766,6 @@
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
@@ -2887,7 +2803,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -2926,7 +2841,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -2962,7 +2876,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -2999,7 +2912,6 @@
           <t>Ordering</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3036,7 +2948,6 @@
           <t>GSB</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3073,7 +2984,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
@@ -3111,7 +3021,6 @@
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
@@ -3149,7 +3058,6 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
@@ -3187,7 +3095,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3200,7 +3107,6 @@
           <t>AU_13</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0.7572</v>
       </c>
@@ -3221,7 +3127,6 @@
           <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>The controllers, through specific
@@ -3259,7 +3164,6 @@
           <t>Business Logic Layer (Services)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Services provide the interface and implementation of all the application's business logic.</t>
@@ -3295,7 +3199,6 @@
           <t>Domain Layer (Models)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Models represent the internal and persistent structure of the system entities, reflecting the
@@ -3332,7 +3235,6 @@
           <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
@@ -3369,7 +3271,6 @@
           <t>Data access layer (Repositories)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>the Repositories are responsible for performing queries on the database.</t>
@@ -3400,7 +3301,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client (frontend), amazon eks</t>
@@ -3436,7 +3336,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>client (frontend), server (backend)</t>
@@ -3472,7 +3371,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -3488,7 +3386,6 @@
           <t>AU_13</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0.7069</v>
       </c>
@@ -3504,7 +3401,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -3545,7 +3441,6 @@
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
@@ -3557,7 +3452,6 @@
           <t>AU_12</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>0.8777</v>
       </c>
@@ -3578,7 +3472,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
@@ -3614,7 +3507,6 @@
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
@@ -3651,7 +3543,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3664,7 +3555,6 @@
           <t>AU_13</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0.8576</v>
       </c>
